--- a/automation/Test Results/Excel/Execution_Summary.xlsx
+++ b/automation/Test Results/Excel/Execution_Summary.xlsx
@@ -31,7 +31,7 @@
     <t>Overall Pass Rate</t>
   </si>
   <si>
-    <t>99.22%</t>
+    <t>100.00%</t>
   </si>
 </sst>
 </file>
@@ -446,7 +446,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -454,7 +454,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">

--- a/automation/Test Results/Excel/Execution_Summary.xlsx
+++ b/automation/Test Results/Excel/Execution_Summary.xlsx
@@ -438,7 +438,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>510</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -446,7 +446,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>510</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">

--- a/automation/Test Results/Excel/Execution_Summary.xlsx
+++ b/automation/Test Results/Excel/Execution_Summary.xlsx
@@ -438,7 +438,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>2040</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -446,7 +446,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>2040</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
